--- a/assets/empty/faang_experiment.xlsx
+++ b/assets/empty/faang_experiment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexey/ebi_projects/faang-portal-frontend/src/assets/empty/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yroochun/Projects/FAANG_TEMPLATES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9844A9F-709E-054F-8468-A11C88C54A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61370CF9-10A7-B644-A8B6-A3FD9ED7A238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
+    <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="19060" activeTab="15" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
   </bookViews>
   <sheets>
     <sheet name="submission" sheetId="13" r:id="rId1"/>
@@ -26,13 +26,17 @@
     <sheet name="bs-seq" sheetId="6" r:id="rId11"/>
     <sheet name="em-seq" sheetId="16" r:id="rId12"/>
     <sheet name="atac-seq" sheetId="7" r:id="rId13"/>
-    <sheet name="scrna-seq" sheetId="14" r:id="rId14"/>
-    <sheet name="cage-seq" sheetId="15" r:id="rId15"/>
-    <sheet name="faang_field_values" sheetId="2" state="hidden" r:id="rId16"/>
+    <sheet name="scatac-seq" sheetId="17" r:id="rId14"/>
+    <sheet name="scrna-seq" sheetId="14" r:id="rId15"/>
+    <sheet name="cage-seq" sheetId="15" r:id="rId16"/>
+    <sheet name="faang_field_values" sheetId="2" r:id="rId17"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'experiment ena'!$B$1:$B$61</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -49,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="349">
   <si>
     <t>Sample Descriptor</t>
   </si>
@@ -963,30 +967,30 @@
     <t>ISO-Seq</t>
   </si>
   <si>
+    <t>Amplification Method</t>
+  </si>
+  <si>
+    <t>End Bias</t>
+  </si>
+  <si>
+    <t>Library Strand</t>
+  </si>
+  <si>
+    <t>Spike In</t>
+  </si>
+  <si>
+    <t>Spike In Dilution Or Concentration</t>
+  </si>
+  <si>
+    <t>Sequencing Protocol</t>
+  </si>
+  <si>
     <t>Library Construction</t>
   </si>
   <si>
     <t>Primer</t>
   </si>
   <si>
-    <t>Amplification Method</t>
-  </si>
-  <si>
-    <t>End Bias</t>
-  </si>
-  <si>
-    <t>Library Strand</t>
-  </si>
-  <si>
-    <t>Spike In</t>
-  </si>
-  <si>
-    <t>Spike In Dilution Or Concentration</t>
-  </si>
-  <si>
-    <t>Sequencing Protocol</t>
-  </si>
-  <si>
     <t>CAGE Protocol</t>
   </si>
   <si>
@@ -1021,13 +1025,88 @@
   </si>
   <si>
     <t>NextSeq 2000</t>
+  </si>
+  <si>
+    <t>scRNA-seq</t>
+  </si>
+  <si>
+    <t>snATAC-seq</t>
+  </si>
+  <si>
+    <t>scATAC-seq assay type</t>
+  </si>
+  <si>
+    <t>scATAC-seq sample storage processing</t>
+  </si>
+  <si>
+    <t>AQUA-FAANG</t>
+  </si>
+  <si>
+    <t>GENE-SWitCH</t>
+  </si>
+  <si>
+    <t>BovReg</t>
+  </si>
+  <si>
+    <t>Bovine-FAANG</t>
+  </si>
+  <si>
+    <t>EFFICACE</t>
+  </si>
+  <si>
+    <t>GEroNIMO</t>
+  </si>
+  <si>
+    <t>RUMIGEN</t>
+  </si>
+  <si>
+    <t>Equine-FAANG</t>
+  </si>
+  <si>
+    <t>Holoruminant</t>
+  </si>
+  <si>
+    <t>USPIGFAANG</t>
+  </si>
+  <si>
+    <t>scATAC-seq sample storage</t>
+  </si>
+  <si>
+    <t>scATAC-seq secondary project</t>
+  </si>
+  <si>
+    <t>Transposed DNA Sequence File Read Index</t>
+  </si>
+  <si>
+    <t>Cell Barcode Read</t>
+  </si>
+  <si>
+    <t>Sample Index Read</t>
+  </si>
+  <si>
+    <t>Nuclei Acid Molecule</t>
+  </si>
+  <si>
+    <t>Nucleic Acid Source</t>
+  </si>
+  <si>
+    <t>Sequencing Method</t>
+  </si>
+  <si>
+    <t>Kit Retail Name</t>
+  </si>
+  <si>
+    <t>Kit Manufacturer</t>
+  </si>
+  <si>
+    <t>Library Construction Method</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1076,6 +1155,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1097,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1109,6 +1195,7 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1129,6 +1216,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="limitedValuesList"/>
       <sheetName val="faang_field_values"/>
@@ -1174,9 +1264,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1214,7 +1304,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1320,7 +1410,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1462,7 +1552,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1471,13 +1561,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{099D7B85-2870-7F44-9DA4-846DC9F871C9}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>248</v>
       </c>
@@ -1491,7 +1581,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38584B3-9902-4E4A-AF0D-04428F33785F}">
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -1532,7 +1622,7 @@
     <col min="37" max="37" width="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1645,34 +1735,53 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="AA2" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{4F13BE38-9FE0-DA43-B2B7-8965729F8B7A}">
+      <formula1>"Tn5 tagmentation, Ligation, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{323CFD0F-B197-B24E-BA52-BB160C681B44}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{B1ADF4A5-307E-0D48-9A40-14BF89476C7F}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{B9CC8377-8B86-3746-9D9C-DD8E5F9E739C}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0B215F54-C5D1-FC4D-B208-8294FEDD23F9}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{EA15EFDE-C0AF-3048-8AF7-BDF3DA1099D3}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$2:$L$2</xm:f>
           </x14:formula1>
           <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{149ADD08-0675-8F41-AA5B-1434A15C4AB5}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EC9C2F5A-B88C-2640-84B8-B7F95D317ED0}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E9A205B3-85D5-D34F-A7BE-9347E00C61B7}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
           </x14:formula1>
           <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E442E21B-D329-C249-BDDC-EAA20E22441E}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1683,7 +1792,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F4B06E-FD05-0A45-81D7-CD289FD919BD}">
   <dimension ref="A1:AH2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -1721,7 +1830,7 @@
     <col min="34" max="34" width="30.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1825,22 +1934,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{280AB9D4-00A2-7E40-99AB-4094FB0D3A77}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{254D7375-3D64-B74E-AE39-C4360D7DF82C}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{9E065262-F008-A447-A432-8DE6F306D34D}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{C460B755-FA9F-7840-99D5-541E618B4DE1}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{043F7D34-6A6D-F84C-858C-9D21F12EA23D}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$2:$L$2</xm:f>
@@ -1849,7 +1962,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8A075E93-1E3B-3E4E-8365-12FF7E80486B}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
@@ -1859,6 +1972,18 @@
           </x14:formula1>
           <xm:sqref>AB2</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AEDE55A6-D123-6B42-A697-1F07C4AAEE6E}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B67651C-4E66-394E-8234-9C04E9901223}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -1866,45 +1991,47 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF0BD7B-344D-684C-9B7E-439F085A320C}">
-  <dimension ref="A1:AF1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CD042A-2E73-AB48-8641-C39B87E182FC}">
+  <dimension ref="A1:AF4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="37.1640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="30.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2002,15 +2129,68 @@
         <v>318</v>
       </c>
     </row>
+    <row r="2" spans="1:32">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+    </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{845EE151-272D-8143-B5A2-0F3458274E9F}">
+      <formula1>"whole-genome, selected genomic regions, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{61DF16C6-56F8-294F-BEFB-6EAC3342C55E}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{E2B944B8-D6C7-3B49-9F29-7D08D18468AB}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{F865F607-DEBA-6D4A-B065-6012D6761ADF}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7026DBAA-0286-0546-BB40-3823869E6808}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B9458E38-BEDA-9848-A6FC-68E3507A4B5A}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{68E5678B-B038-3A45-A616-4BD8B23BFBEB}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F3A152FC-B403-E546-AC1F-A5F482272F68}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$25:$L$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F024D0-A71F-1D4F-B7B8-1935431836D0}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2042,7 +2222,7 @@
     <col min="28" max="28" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2128,22 +2308,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{9BC09621-A5FE-094A-A4A4-45B5E7048041}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{51317A09-E22E-8042-B8C2-A91DECF80DAC}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{7C4A2AB4-F62C-824F-BCCC-8275BE80E1A5}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{3F11DC62-E35E-5648-B844-5543DDBC83A1}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8E8680DA-052A-464F-8853-7A707E219755}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$2:$L$2</xm:f>
@@ -2152,9 +2336,21 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D90F9425-0FCF-3F42-B5AD-EB00FB185850}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{450CAAC2-262B-3D4D-B43F-7A393927CD3D}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E4CD5FE1-2620-2241-A80F-EED59E103513}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2163,9 +2359,210 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79CF2441-AB9C-F644-90EE-34F00FC128F1}">
-  <dimension ref="A1:AO1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F3F0A2-0F3F-D140-8D28-9CEC0151DBD6}">
+  <dimension ref="A1:AM1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="39" width="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="AE1" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="AF1" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="AG1" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="AH1" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI1" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="AJ1" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="AK1" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="AL1" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="AM1" s="9"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{B13F4C4A-6BD1-DA4F-9A94-F4BB50FD2A88}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{8952B455-BA53-5245-A558-53D00808D12B}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{2AEE7C2D-4829-254D-9274-E81EE2CC0BC7}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2" xr:uid="{2335A399-1068-E147-B715-42BAA874050D}">
+      <formula1>"SO:0001747, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{49340548-6FAB-754B-8D85-613DC273DAB9}">
+      <formula1>"R1/R3, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{84B29063-D5FA-B04D-9C6A-38816954ABC9}">
+      <formula1>"R2, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2" xr:uid="{E4E7BC4D-6195-634D-BACD-0D57DD1C62AC}">
+      <formula1>"I1, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DAD5BB5-2950-0048-BD7E-9416EB636803}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$22:$R$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CF22FA4F-46C9-2041-A4CA-C69A37A22C65}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7CDE2CD1-D2BB-684A-8AF3-5AF95356F669}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2E5EB13B-2C30-F84A-9883-3C9BDA72E7E0}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$25:$L$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915533FD-907A-6F4D-A3D0-6F3E67DCA835}">
+  <dimension ref="A1:AO2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2195,8 +2592,8 @@
     <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26" customWidth="1"/>
+    <col min="30" max="30" width="21" customWidth="1"/>
     <col min="31" max="31" width="18" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -2209,7 +2606,7 @@
     <col min="41" max="41" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2292,34 +2689,34 @@
         <v>87</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="AE1" s="8" t="s">
         <v>321</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>67</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>68</v>
@@ -2334,15 +2731,80 @@
         <v>69</v>
       </c>
     </row>
+    <row r="2" spans="1:41">
+      <c r="E2" s="2"/>
+    </row>
   </sheetData>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{4C8DC41F-363B-1A4A-9FFB-60E491A6B435}">
+      <formula1>"Smart-Seq2, Drop-Seq, 10X v1, 10X v2, 10X v3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{DBC0E0FA-04AF-F646-AF27-A5C56962B791}">
+      <formula1>"oligo-dT, random"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{FE30E2CC-BD3C-914B-BA38-2E0029F8CBCE}">
+      <formula1>"PCR, in vitro transcription, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2" xr:uid="{E58F366C-B5D3-CE4F-AA48-66D3CB62AF2E}">
+      <formula1>"3 prime tag, 5 prime tag, full-length, none, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{AB888E16-3318-3343-9FE2-C3E68A712871}">
+      <formula1>"first (antisense), second (sense), both, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2" xr:uid="{294E17B4-67BD-FF4D-9FE2-07B077D7526F}">
+      <formula1>"none, External RNA Controls Consortium (ERCC), restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2" xr:uid="{EBE8D388-778D-954D-9730-5D3AFBCEE867}">
+      <formula1>"sense, antisense, mate 1 sense, mate 2 sense, non-stranded, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{95E7FFA4-E720-A84B-850C-33127D5C1306}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{E90DC451-127C-F145-B67F-FE1BF8AA3975}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{A2954073-076C-7D4E-A8A5-D0E719EBC768}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35EB2A9F-D130-DF42-A1AC-1C532A6FA469}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6B5B0EC7-6D86-CC4E-AA39-B5945B7E47DE}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C9C1A2B7-C3DB-0848-95EB-9412A9F13C59}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3F9E4D6C-D318-5E47-ABDC-3F957B80A25C}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$25:$L$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97421E41-8CEC-7C40-9236-96710DA47BAA}">
-  <dimension ref="A1:AI1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2353DD-D244-1A4B-A630-CADDC4768141}">
+  <dimension ref="A1:AI2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2380,7 +2842,7 @@
     <col min="35" max="35" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2487,17 +2949,61 @@
         <v>69</v>
       </c>
     </row>
+    <row r="2" spans="1:35">
+      <c r="E2" s="2"/>
+    </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{D35199EA-8F2D-F74F-B5D7-590C34074504}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{8A15D947-2B37-8249-8167-7E6F0F51D6CA}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{6BC448C9-8DAC-4E44-96D7-3AC72411F5F6}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{287312AD-AC2C-4842-9F8D-712F3AF247FD}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{623C33EF-D501-2641-A8A6-BE5C911E1AC1}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{46F8DF94-188F-A644-97AD-5849D2AA776A}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B91F2BE1-72C8-774E-AB1C-E356CD496D4F}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$25:$L$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BFC3F93-CB0B-BF48-9B11-5793D4DCF38D}">
-  <dimension ref="A1:BC1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BC997"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -2551,7 +3057,7 @@
     <col min="54" max="54" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="15.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
@@ -2563,41 +3069,47 @@
         <v>23</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="O1" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
+      <c r="Q1" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
@@ -2608,7 +3120,7 @@
       <c r="Z1" s="5"/>
       <c r="AA1" s="5"/>
     </row>
-    <row r="2" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" ht="15.75" customHeight="1">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -2643,7 +3155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" ht="15.75" customHeight="1">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -2672,7 +3184,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" ht="15.75" customHeight="1">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -2680,8 +3192,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="6" spans="1:36" ht="15.75" customHeight="1">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -2695,8 +3207,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="8" spans="1:36" ht="15.75" customHeight="1">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2719,8 +3231,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:36" ht="15.75" customHeight="1">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -2731,8 +3243,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:36" ht="15.75" customHeight="1">
       <c r="A12" t="s">
         <v>117</v>
       </c>
@@ -2842,7 +3354,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" ht="15.75" customHeight="1">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -2871,7 +3383,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" ht="15.75" customHeight="1">
       <c r="A14" t="s">
         <v>157</v>
       </c>
@@ -2966,7 +3478,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" ht="15.75" customHeight="1">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -2974,7 +3486,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" ht="15.75" customHeight="1">
       <c r="A16" t="s">
         <v>187</v>
       </c>
@@ -3006,7 +3518,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="17" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:55" ht="15.75" customHeight="1">
       <c r="A17" t="s">
         <v>196</v>
       </c>
@@ -3173,7 +3685,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="18" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:55" ht="15.75" customHeight="1">
       <c r="A18" t="s">
         <v>261</v>
       </c>
@@ -3181,7 +3693,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="19" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:55" ht="15.75" customHeight="1">
       <c r="A19" t="s">
         <v>263</v>
       </c>
@@ -3228,7 +3740,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:55" ht="15.75" customHeight="1">
       <c r="A20" t="s">
         <v>277</v>
       </c>
@@ -3302,988 +3814,1135 @@
         <v>299</v>
       </c>
     </row>
-    <row r="21" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22" t="s">
+        <v>324</v>
+      </c>
+      <c r="P22" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>325</v>
+      </c>
+      <c r="R22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" t="s">
+        <v>47</v>
+      </c>
+      <c r="J23" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C24" t="s">
+        <v>328</v>
+      </c>
+      <c r="D24" t="s">
+        <v>329</v>
+      </c>
+      <c r="E24" t="s">
+        <v>330</v>
+      </c>
+      <c r="F24" t="s">
+        <v>331</v>
+      </c>
+      <c r="G24" t="s">
+        <v>332</v>
+      </c>
+      <c r="H24" t="s">
+        <v>333</v>
+      </c>
+      <c r="I24" t="s">
+        <v>334</v>
+      </c>
+      <c r="J24" t="s">
+        <v>335</v>
+      </c>
+      <c r="K24" t="s">
+        <v>336</v>
+      </c>
+      <c r="L24" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sAuiyFEGJJ1sKigCSPZwC7GiIGVLwfMRquQSiZucDzFMEd4LyTzcSo4jqfoCzIgaCzI1iNGljxasutRFlvdT1A==" saltValue="99lYszZxeigXcrEyiP+b9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4291,7 +4950,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D9D0EF-48E8-0848-8FC3-887221A9CD61}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.1640625" bestFit="1" customWidth="1"/>
@@ -4299,7 +4958,7 @@
     <col min="4" max="4" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>93</v>
       </c>
@@ -4333,7 +4992,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75EBC70-0652-FD45-91E3-795D61059D70}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -4349,7 +5008,7 @@
     <col min="12" max="12" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>248</v>
       </c>
@@ -4387,7 +5046,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4433,7 +5092,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F098638-7041-8742-A382-2ACA2B20888B}">
   <dimension ref="A1:O61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
@@ -4452,7 +5111,7 @@
     <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4499,7 +5158,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4516,7 +5175,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4533,7 +5192,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4550,7 +5209,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -4567,7 +5226,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -4584,7 +5243,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -4601,7 +5260,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4618,7 +5277,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4635,7 +5294,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4652,7 +5311,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4669,7 +5328,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -4686,7 +5345,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4703,7 +5362,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -4720,7 +5379,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -4737,7 +5396,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -4754,7 +5413,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -4771,7 +5430,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -4788,7 +5447,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4805,7 +5464,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4822,7 +5481,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4839,7 +5498,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4856,7 +5515,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4873,7 +5532,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4890,7 +5549,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4907,7 +5566,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -4924,7 +5583,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -4941,7 +5600,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -4958,7 +5617,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -4975,7 +5634,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -4992,7 +5651,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -5009,7 +5668,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -5026,7 +5685,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -5043,7 +5702,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -5060,7 +5719,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -5077,7 +5736,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -5094,7 +5753,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -5111,7 +5770,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -5128,7 +5787,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -5145,7 +5804,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -5162,7 +5821,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -5179,7 +5838,7 @@
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -5196,7 +5855,7 @@
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -5213,7 +5872,7 @@
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -5230,7 +5889,7 @@
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -5247,7 +5906,7 @@
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5264,7 +5923,7 @@
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5281,7 +5940,7 @@
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -5298,7 +5957,7 @@
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -5315,7 +5974,7 @@
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5332,7 +5991,7 @@
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5349,7 +6008,7 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5366,7 +6025,7 @@
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5383,7 +6042,7 @@
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5400,7 +6059,7 @@
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -5417,7 +6076,7 @@
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -5434,7 +6093,7 @@
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -5451,7 +6110,7 @@
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -5468,7 +6127,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -5485,7 +6144,7 @@
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -5502,7 +6161,7 @@
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -5529,31 +6188,31 @@
           <x14:formula1>
             <xm:f>faang_field_values!$A$12:$AJ$12</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G61 G2</xm:sqref>
+          <xm:sqref>G2:G61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{035246E8-AB62-BB40-94E1-ED3189C6D0EA}">
           <x14:formula1>
             <xm:f>faang_field_values!$A$13:$I$13</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H61 H2</xm:sqref>
+          <xm:sqref>H2:H61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E6C1D42E-693B-BD49-8244-66A86F48A696}">
           <x14:formula1>
             <xm:f>faang_field_values!$A$14:$AE$14</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I61 I2</xm:sqref>
+          <xm:sqref>I2:I61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{BF78C95C-71B6-4545-B3F3-9F9F12D5AEEC}">
           <x14:formula1>
             <xm:f>faang_field_values!$A$15:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>J3:J61 J2</xm:sqref>
+          <xm:sqref>J2:J61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{2F42C0F1-99A9-1248-A8D8-0FDC07FDD21D}">
           <x14:formula1>
             <xm:f>faang_field_values!$A$16:$J$16</xm:f>
           </x14:formula1>
-          <xm:sqref>N3:N61 N2</xm:sqref>
+          <xm:sqref>N2:N61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{6A4DD186-42BE-B14E-BF5C-0EAA7E5FF656}">
           <x14:formula1>
@@ -5561,7 +6220,7 @@
           </x14:formula1>
           <xm:sqref>O3:O61</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{6E48A385-1211-CF4E-8AE0-ACA32D191723}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{EA39BA85-9002-7E40-8848-8844945AE72E}">
           <x14:formula1>
             <xm:f>faang_field_values!$A$17:$BC$17</xm:f>
           </x14:formula1>
@@ -5576,9 +6235,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A64CF7-9397-CE4E-90CF-9FB7735D75EC}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
@@ -5610,7 +6269,7 @@
     <col min="30" max="30" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5702,39 +6361,58 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{95AC9D10-AA72-0A4F-A232-3FDF91F98DB5}">
+      <formula1>"reduced representation, none"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{9F8BA4A7-D0B0-C847-BAC2-69366FE87926}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 W2 U2" xr:uid="{1EBAD764-9B36-7345-9CE0-AD8322EC6DD4}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2" xr:uid="{378880C5-C6CC-5446-853A-D223A643981D}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C62E301D-8248-B944-9FDB-59C9C09B8F83}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{14E138D7-4850-0A4C-A78C-04C49A19DC51}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$2:$L$2</xm:f>
           </x14:formula1>
           <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{635BC845-20CB-1744-BC79-5C578ABBBA5A}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BEBD69DF-17F0-D744-A345-E04E060CE5D3}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$10:$D$10</xm:f>
           </x14:formula1>
           <xm:sqref>AC2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FDF140C2-84F6-AA42-94F1-5C6A583FEC12}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8937FC53-71A1-BD42-9595-9AEDE1992A8E}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AC0CB1F0-67D7-674C-A479-99D65A8AFE1B}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5745,45 +6423,42 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15FFCCF9-4CDE-C54B-AD24-35A7E281B9D4}">
   <dimension ref="A1:AJ61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="189.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="110.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="68" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="68" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="26.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="15" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="37.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="42.5" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="37" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="189.1640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="34" max="35" width="22" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5893,31 +6568,23 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
       <c r="L2" s="2"/>
       <c r="M2" s="6"/>
-      <c r="N2" s="2"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="6"/>
-      <c r="U2" s="2"/>
       <c r="V2" s="6"/>
-      <c r="W2" s="2"/>
       <c r="X2" s="2"/>
+      <c r="Y2"/>
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
       <c r="AB2" s="3"/>
@@ -5930,7 +6597,7 @@
       <c r="AI2" s="6"/>
       <c r="AJ2" s="6"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5967,7 +6634,7 @@
       <c r="AI3" s="6"/>
       <c r="AJ3" s="6"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6004,7 +6671,7 @@
       <c r="AI4" s="6"/>
       <c r="AJ4" s="6"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6041,7 +6708,7 @@
       <c r="AI5" s="6"/>
       <c r="AJ5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -6078,7 +6745,7 @@
       <c r="AI6" s="6"/>
       <c r="AJ6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -6115,7 +6782,7 @@
       <c r="AI7" s="6"/>
       <c r="AJ7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -6152,7 +6819,7 @@
       <c r="AI8" s="6"/>
       <c r="AJ8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6189,7 +6856,7 @@
       <c r="AI9" s="6"/>
       <c r="AJ9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -6226,7 +6893,7 @@
       <c r="AI10" s="6"/>
       <c r="AJ10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -6263,7 +6930,7 @@
       <c r="AI11" s="6"/>
       <c r="AJ11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6300,7 +6967,7 @@
       <c r="AI12" s="6"/>
       <c r="AJ12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -6337,7 +7004,7 @@
       <c r="AI13" s="6"/>
       <c r="AJ13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -6374,7 +7041,7 @@
       <c r="AI14" s="6"/>
       <c r="AJ14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -6411,7 +7078,7 @@
       <c r="AI15" s="6"/>
       <c r="AJ15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -6448,7 +7115,7 @@
       <c r="AI16" s="6"/>
       <c r="AJ16" s="6"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -6485,7 +7152,7 @@
       <c r="AI17" s="6"/>
       <c r="AJ17" s="6"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -6522,7 +7189,7 @@
       <c r="AI18" s="6"/>
       <c r="AJ18" s="6"/>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -6559,7 +7226,7 @@
       <c r="AI19" s="6"/>
       <c r="AJ19" s="6"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -6596,7 +7263,7 @@
       <c r="AI20" s="6"/>
       <c r="AJ20" s="6"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -6633,7 +7300,7 @@
       <c r="AI21" s="6"/>
       <c r="AJ21" s="6"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -6670,7 +7337,7 @@
       <c r="AI22" s="6"/>
       <c r="AJ22" s="6"/>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -6707,7 +7374,7 @@
       <c r="AI23" s="6"/>
       <c r="AJ23" s="6"/>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -6744,7 +7411,7 @@
       <c r="AI24" s="6"/>
       <c r="AJ24" s="6"/>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -6781,7 +7448,7 @@
       <c r="AI25" s="6"/>
       <c r="AJ25" s="6"/>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -6818,7 +7485,7 @@
       <c r="AI26" s="6"/>
       <c r="AJ26" s="6"/>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -6855,7 +7522,7 @@
       <c r="AI27" s="6"/>
       <c r="AJ27" s="6"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -6892,7 +7559,7 @@
       <c r="AI28" s="6"/>
       <c r="AJ28" s="6"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -6929,7 +7596,7 @@
       <c r="AI29" s="6"/>
       <c r="AJ29" s="6"/>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -6966,7 +7633,7 @@
       <c r="AI30" s="6"/>
       <c r="AJ30" s="6"/>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -7003,7 +7670,7 @@
       <c r="AI31" s="6"/>
       <c r="AJ31" s="6"/>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -7040,7 +7707,7 @@
       <c r="AI32" s="6"/>
       <c r="AJ32" s="6"/>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -7077,7 +7744,7 @@
       <c r="AI33" s="6"/>
       <c r="AJ33" s="6"/>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -7114,7 +7781,7 @@
       <c r="AI34" s="6"/>
       <c r="AJ34" s="6"/>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -7151,7 +7818,7 @@
       <c r="AI35" s="6"/>
       <c r="AJ35" s="6"/>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -7188,7 +7855,7 @@
       <c r="AI36" s="6"/>
       <c r="AJ36" s="6"/>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -7225,7 +7892,7 @@
       <c r="AI37" s="6"/>
       <c r="AJ37" s="6"/>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -7262,7 +7929,7 @@
       <c r="AI38" s="6"/>
       <c r="AJ38" s="6"/>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -7299,7 +7966,7 @@
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -7336,7 +8003,7 @@
       <c r="AI40" s="6"/>
       <c r="AJ40" s="6"/>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -7373,7 +8040,7 @@
       <c r="AI41" s="6"/>
       <c r="AJ41" s="6"/>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -7410,7 +8077,7 @@
       <c r="AI42" s="6"/>
       <c r="AJ42" s="6"/>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -7447,7 +8114,7 @@
       <c r="AI43" s="6"/>
       <c r="AJ43" s="6"/>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -7484,7 +8151,7 @@
       <c r="AI44" s="6"/>
       <c r="AJ44" s="6"/>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -7521,7 +8188,7 @@
       <c r="AI45" s="6"/>
       <c r="AJ45" s="6"/>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -7558,7 +8225,7 @@
       <c r="AI46" s="6"/>
       <c r="AJ46" s="6"/>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7595,7 +8262,7 @@
       <c r="AI47" s="6"/>
       <c r="AJ47" s="6"/>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -7632,7 +8299,7 @@
       <c r="AI48" s="6"/>
       <c r="AJ48" s="6"/>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -7669,7 +8336,7 @@
       <c r="AI49" s="6"/>
       <c r="AJ49" s="6"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -7706,7 +8373,7 @@
       <c r="AI50" s="6"/>
       <c r="AJ50" s="6"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -7743,7 +8410,7 @@
       <c r="AI51" s="6"/>
       <c r="AJ51" s="6"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -7780,7 +8447,7 @@
       <c r="AI52" s="6"/>
       <c r="AJ52" s="6"/>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -7817,7 +8484,7 @@
       <c r="AI53" s="6"/>
       <c r="AJ53" s="6"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -7854,7 +8521,7 @@
       <c r="AI54" s="6"/>
       <c r="AJ54" s="6"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -7891,7 +8558,7 @@
       <c r="AI55" s="6"/>
       <c r="AJ55" s="6"/>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -7928,7 +8595,7 @@
       <c r="AI56" s="6"/>
       <c r="AJ56" s="6"/>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -7965,7 +8632,7 @@
       <c r="AI57" s="6"/>
       <c r="AJ57" s="6"/>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -8002,7 +8669,7 @@
       <c r="AI58" s="6"/>
       <c r="AJ58" s="6"/>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -8039,7 +8706,7 @@
       <c r="AI59" s="6"/>
       <c r="AJ59" s="6"/>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -8076,7 +8743,7 @@
       <c r="AI60" s="6"/>
       <c r="AJ60" s="6"/>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -8115,15 +8782,27 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{1B337130-3338-8443-9BCF-59D1509F6ABF}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{B1D9DA5F-537B-454B-9423-5E0010795182}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{57F4A150-AC0E-7548-B8A6-56CD6758C86E}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{90261B97-D2DD-1648-87CC-7CFE09E7C764}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$2:$L$2</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F61</xm:sqref>
+          <xm:sqref>F3:F61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{608D7F49-F2E3-CD42-A9FD-5F1495A620D7}">
           <x14:formula1>
@@ -8131,29 +8810,41 @@
           </x14:formula1>
           <xm:sqref>G3:G61</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E7490766-17A0-D640-9F4A-3E238B171AB0}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E61</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{B36E592A-6530-D549-8D99-9C660A44BBD6}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{23AB4F37-0822-7440-84E5-5BCBEF7BB1F5}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$8:$H$8</xm:f>
           </x14:formula1>
           <xm:sqref>AG2:AG61</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E3E48697-7DD6-384E-8B19-F3BA3019A838}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BEEA9DAE-3239-F94B-8CB8-0A2D96481E5D}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$1:$O$1</xm:f>
           </x14:formula1>
+          <xm:sqref>E3:E61</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E4A6A670-E8DC-944B-AD74-04F0CB70D152}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
+          </x14:formula1>
           <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C23ACA45-7340-A944-96E5-422D5A4140A9}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A623FDE-408D-9645-8B27-150EF01919C7}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F7E30579-87B4-F840-841C-79832701B902}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$25:$L$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8164,7 +8855,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406AA4AD-A9F2-684E-89D7-0B0303DBBB91}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -8198,7 +8889,7 @@
     <col min="30" max="30" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8290,16 +8981,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{5EDE529C-0371-F64C-97F5-C5BEBF963C3D}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{66FBED7B-B609-1C43-9B48-56AA0E6BE5B8}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{1A62C303-B7A3-2C43-89F6-3689C042A2D9}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{B3E0CA1B-4D6D-6149-8682-9DB682EFDFE0}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$3:$J$3</xm:f>
@@ -8312,11 +9014,17 @@
           </x14:formula1>
           <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{338EEE75-D370-8A4D-9140-60BFB5E3F1FF}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{59C8F82B-DBA5-0344-8D5A-E93055475182}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E728C318-43EC-4A40-BEDE-EEF9E618C2CB}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8327,7 +9035,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7681A6-8E41-9842-885B-F7FC7045D433}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -8360,7 +9068,7 @@
     <col min="29" max="29" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8448,19 +9156,29 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{93FE74FB-7105-DF4A-B552-F93B1B63CD60}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{A421E24F-8225-F64B-A541-B48A7AA38AD5}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{7A8934A8-A0D9-3E41-B147-59893101B388}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D5E3DB2-EC39-3C4F-9821-F1F8EEDE1843}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
@@ -8470,11 +9188,17 @@
           </x14:formula1>
           <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{18764BFC-F0B5-C742-A294-27BA360B391E}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{460F1628-E581-764C-B643-FF5770352022}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
           </x14:formula1>
           <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ADB33EAF-2088-7242-A8C6-C0DB95F55635}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8485,7 +9209,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BD49F3-4725-E748-A029-B6B285E09FD7}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -8520,7 +9244,7 @@
     <col min="31" max="31" width="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8615,34 +9339,53 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="AA2" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{9FEAF58E-5FA8-7647-9622-3CF659A8C882}">
+      <formula1>"Tn5 tagmentation, Ligation, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{5AB5EF07-C4CA-304C-9D54-34796D03C850}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 N2 U2 W2" xr:uid="{76F350EA-FB3C-2546-AD6F-68832FC421AF}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{50826ADF-49AB-8341-AEBF-69D9D397E007}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E5794F02-B71D-B847-983B-F96FCA4C0E87}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8580A94C-226D-B947-94D3-CD9D72A3F567}">
           <x14:formula1>
             <xm:f>faang_field_values!$C$2:$L$2</xm:f>
           </x14:formula1>
           <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EE19D93F-F23D-0B42-86C6-1CE61152BE0E}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7D36CDBE-08E3-B047-AA62-D1ACBAC653D2}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DEBF8BA2-D922-AA44-A715-E1473227A2DC}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9A134B09-F2B2-9148-9C79-757DCC84A731}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/assets/empty/faang_experiment.xlsx
+++ b/assets/empty/faang_experiment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yroochun/Projects/FAANG_TEMPLATES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61370CF9-10A7-B644-A8B6-A3FD9ED7A238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162005C1-2060-EC43-859C-259687B4C528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="19060" activeTab="15" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="16" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
   </bookViews>
   <sheets>
     <sheet name="submission" sheetId="13" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="348">
   <si>
     <t>Sample Descriptor</t>
   </si>
@@ -1031,9 +1031,6 @@
   </si>
   <si>
     <t>snATAC-seq</t>
-  </si>
-  <si>
-    <t>scATAC-seq assay type</t>
   </si>
   <si>
     <t>scATAC-seq sample storage processing</t>
@@ -2468,34 +2465,34 @@
         <v>82</v>
       </c>
       <c r="AC1" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="AD1" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AH1" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AI1" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>346</v>
-      </c>
-      <c r="AJ1" s="9" t="s">
-        <v>347</v>
       </c>
       <c r="AK1" s="9" t="s">
         <v>309</v>
       </c>
       <c r="AL1" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AM1" s="9"/>
     </row>
@@ -2531,7 +2528,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DAD5BB5-2950-0048-BD7E-9416EB636803}">
           <x14:formula1>
-            <xm:f>faang_field_values!$C$22:$R$22</xm:f>
+            <xm:f>faang_field_values!$C$1:$R$1</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
@@ -3816,61 +3813,11 @@
     </row>
     <row r="21" spans="1:55" ht="15.75" customHeight="1"/>
     <row r="22" spans="1:55" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" t="s">
-        <v>28</v>
-      </c>
-      <c r="L22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M22" t="s">
-        <v>30</v>
-      </c>
-      <c r="N22" t="s">
-        <v>15</v>
-      </c>
-      <c r="O22" t="s">
-        <v>324</v>
-      </c>
-      <c r="P22" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>325</v>
-      </c>
-      <c r="R22" t="s">
-        <v>76</v>
-      </c>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:55" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
@@ -3902,42 +3849,42 @@
     </row>
     <row r="24" spans="1:55" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C24" t="s">
+        <v>327</v>
+      </c>
+      <c r="D24" t="s">
         <v>328</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>329</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>330</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>331</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>332</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>333</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>334</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>335</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>336</v>
-      </c>
-      <c r="L24" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="25" spans="1:55" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C25" t="s">
         <v>34</v>

--- a/assets/empty/faang_experiment.xlsx
+++ b/assets/empty/faang_experiment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yroochun/Projects/FAANG_TEMPLATES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yroochun/Projects/faang-validator-frontend/assets/empty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162005C1-2060-EC43-859C-259687B4C528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA5B974-4D27-A645-B9AE-B72400004A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="16" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
+    <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="19060" activeTab="4" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
   </bookViews>
   <sheets>
     <sheet name="submission" sheetId="13" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <sheet name="scatac-seq" sheetId="17" r:id="rId14"/>
     <sheet name="scrna-seq" sheetId="14" r:id="rId15"/>
     <sheet name="cage-seq" sheetId="15" r:id="rId16"/>
-    <sheet name="faang_field_values" sheetId="2" r:id="rId17"/>
+    <sheet name="faang_field_values" sheetId="2" state="hidden" r:id="rId17"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId18"/>
@@ -4890,6 +4890,7 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="C8Udtk83sPk6mqnur4v/XDEdRC/g1QFgL/tfZQZzPE2kWfMMKXgHICwZ+nivIIyzqi1xl11kYa1iLy0Y0dyd0A==" saltValue="LlWWW0d7X8iLvmB6iXJKbg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
